--- a/app1/Excelfiles/March2024_5000.xlsx
+++ b/app1/Excelfiles/March2024_5000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,6 +443,10 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -471,12 +475,21 @@
       </c>
     </row>
     <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
